--- a/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0606</v>
+        <v>0.00055</v>
       </c>
       <c r="E2">
-        <v>0.02867</v>
+        <v>-0.0915</v>
       </c>
       <c r="F2">
-        <v>0.079</v>
+        <v>0.121</v>
       </c>
       <c r="G2">
-        <v>0.1225783198653337</v>
+        <v>0.08100394506062049</v>
       </c>
       <c r="H2">
-        <v>0.1225783198653337</v>
+        <v>0.08100394506062049</v>
       </c>
       <c r="I2">
-        <v>0.1066914899716988</v>
+        <v>0.03152437091240074</v>
       </c>
       <c r="J2">
-        <v>0.09075825663635524</v>
+        <v>0.02260177189187236</v>
       </c>
       <c r="K2">
-        <v>11218.22</v>
+        <v>5446.787</v>
       </c>
       <c r="L2">
-        <v>0.05743296376541515</v>
+        <v>0.03481514080005728</v>
       </c>
       <c r="M2">
-        <v>50.74</v>
+        <v>39.7</v>
       </c>
       <c r="N2">
-        <v>0.0004630415459783647</v>
+        <v>0.0003996879011351338</v>
       </c>
       <c r="O2">
-        <v>0.004522999192385246</v>
+        <v>0.007288700659673309</v>
       </c>
       <c r="P2">
-        <v>50.74</v>
+        <v>39.7</v>
       </c>
       <c r="Q2">
-        <v>0.0004630415459783647</v>
+        <v>0.0003996879011351338</v>
       </c>
       <c r="R2">
-        <v>0.004522999192385246</v>
+        <v>0.007288700659673309</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>31151.06</v>
+        <v>26942</v>
       </c>
       <c r="V2">
-        <v>0.2842773941912652</v>
+        <v>0.2712441166847047</v>
       </c>
       <c r="W2">
-        <v>0.08925223911685065</v>
+        <v>0.04265801188085191</v>
       </c>
       <c r="X2">
-        <v>0.0443648771700142</v>
+        <v>0.08120232024473512</v>
       </c>
       <c r="Y2">
-        <v>0.04488736194683645</v>
+        <v>-0.0385443083638832</v>
       </c>
       <c r="Z2">
-        <v>1.623066841763962</v>
+        <v>1.245676624963583</v>
       </c>
       <c r="AA2">
-        <v>-0.08502086875869531</v>
+        <v>0.01579015132517658</v>
       </c>
       <c r="AB2">
-        <v>0.04362185373069513</v>
+        <v>0.07231574267378031</v>
       </c>
       <c r="AC2">
-        <v>-0.1288382167262159</v>
+        <v>-0.05657698161453842</v>
       </c>
       <c r="AD2">
-        <v>49821.60000000001</v>
+        <v>46804.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>49821.60000000001</v>
+        <v>46804.6</v>
       </c>
       <c r="AG2">
-        <v>18670.54</v>
+        <v>19862.6</v>
       </c>
       <c r="AH2">
-        <v>0.3125543439392628</v>
+        <v>0.3202896557293025</v>
       </c>
       <c r="AI2">
-        <v>0.2924928845846758</v>
+        <v>0.4031970035414101</v>
       </c>
       <c r="AJ2">
-        <v>0.1455788733191663</v>
+        <v>0.1666463909334752</v>
       </c>
       <c r="AK2">
-        <v>0.1341434973467371</v>
+        <v>0.2228205205868858</v>
       </c>
       <c r="AL2">
-        <v>1557.73</v>
+        <v>1691.34</v>
       </c>
       <c r="AM2">
-        <v>1557.73</v>
+        <v>1691.34</v>
       </c>
       <c r="AN2">
-        <v>2.23229955763176</v>
+        <v>6.953040393491524</v>
       </c>
       <c r="AO2">
-        <v>13.37828121689895</v>
+        <v>2.916001513592773</v>
       </c>
       <c r="AP2">
-        <v>0.8365495725297075</v>
+        <v>2.950681345845595</v>
       </c>
       <c r="AQ2">
-        <v>13.37828121689895</v>
+        <v>2.916001513592773</v>
       </c>
     </row>
     <row r="3">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06900000000000001</v>
+        <v>0.0868</v>
       </c>
       <c r="E3">
-        <v>-0.00136</v>
+        <v>0.0858</v>
       </c>
       <c r="F3">
-        <v>0.13</v>
+        <v>0.138</v>
       </c>
       <c r="G3">
-        <v>0.04879206484693784</v>
+        <v>0.0711707968353536</v>
       </c>
       <c r="H3">
-        <v>0.04879206484693784</v>
+        <v>0.0711707968353536</v>
       </c>
       <c r="I3">
-        <v>0.05258118599491932</v>
+        <v>0.05712562195088512</v>
       </c>
       <c r="J3">
-        <v>0.0389066495414758</v>
+        <v>0.04407599674368774</v>
       </c>
       <c r="K3">
-        <v>1015.3</v>
+        <v>1052.2</v>
       </c>
       <c r="L3">
-        <v>0.02068330484701933</v>
+        <v>0.02219302149487569</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -773,73 +773,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5725.5</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.4702205942740756</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.08481754995655952</v>
+        <v>0.08523495913225919</v>
       </c>
       <c r="X3">
-        <v>0.05665470675171378</v>
+        <v>0.0890388129273384</v>
       </c>
       <c r="Y3">
-        <v>0.02816284320484574</v>
+        <v>-0.003803853795079207</v>
       </c>
       <c r="Z3">
-        <v>3.773873132779285</v>
+        <v>3.594270248961398</v>
       </c>
       <c r="AA3">
-        <v>0.146828759391035</v>
+        <v>0.1584210437891563</v>
       </c>
       <c r="AB3">
-        <v>0.04150633290213191</v>
+        <v>0.07004071486829327</v>
       </c>
       <c r="AC3">
-        <v>0.1053224264889031</v>
+        <v>0.08838032892086303</v>
       </c>
       <c r="AD3">
-        <v>7775.8</v>
+        <v>6652.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7775.8</v>
+        <v>6652.3</v>
       </c>
       <c r="AG3">
-        <v>2050.3</v>
+        <v>6652.3</v>
       </c>
       <c r="AH3">
-        <v>0.3897253408179631</v>
+        <v>0.3566457935708005</v>
       </c>
       <c r="AI3">
-        <v>0.2761233780530244</v>
+        <v>0.3288903171581836</v>
       </c>
       <c r="AJ3">
-        <v>0.144118370646329</v>
+        <v>0.3566457935708005</v>
       </c>
       <c r="AK3">
-        <v>0.09138804819234148</v>
+        <v>0.3288903171581836</v>
       </c>
       <c r="AL3">
-        <v>441.6</v>
+        <v>210.8</v>
       </c>
       <c r="AM3">
-        <v>441.6</v>
+        <v>210.8</v>
       </c>
       <c r="AN3">
-        <v>2.694877659943162</v>
+        <v>2.194754206532497</v>
       </c>
       <c r="AO3">
-        <v>5.844882246376812</v>
+        <v>12.84819734345351</v>
       </c>
       <c r="AP3">
-        <v>0.7105773896166909</v>
+        <v>2.194754206532497</v>
       </c>
       <c r="AQ3">
-        <v>5.844882246376812</v>
+        <v>12.84819734345351</v>
       </c>
     </row>
     <row r="4">
@@ -859,31 +859,31 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0239</v>
+        <v>0.00055</v>
       </c>
       <c r="E4">
-        <v>0.0587</v>
+        <v>-0.0915</v>
       </c>
       <c r="F4">
-        <v>0.028</v>
+        <v>0.104</v>
       </c>
       <c r="G4">
-        <v>0.1553460681517956</v>
+        <v>0.08850706484561131</v>
       </c>
       <c r="H4">
-        <v>0.1553460681517956</v>
+        <v>0.08850706484561131</v>
       </c>
       <c r="I4">
-        <v>0.1328222128636784</v>
+        <v>0.02223291581157267</v>
       </c>
       <c r="J4">
-        <v>0.100198750153524</v>
+        <v>0.01635805683487464</v>
       </c>
       <c r="K4">
-        <v>10105.5</v>
+        <v>4352.8</v>
       </c>
       <c r="L4">
-        <v>0.0727482803675748</v>
+        <v>0.04107093152171349</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -907,73 +907,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>25424.2</v>
+        <v>26315</v>
       </c>
       <c r="V4">
-        <v>0.2647446864564124</v>
+        <v>0.3050091508540604</v>
       </c>
       <c r="W4">
-        <v>0.1152979914840017</v>
+        <v>0.04600188961998347</v>
       </c>
       <c r="X4">
-        <v>0.0526127487978692</v>
+        <v>0.08677820751132019</v>
       </c>
       <c r="Y4">
-        <v>0.06268524268613249</v>
+        <v>-0.04077631789133672</v>
       </c>
       <c r="Z4">
-        <v>1.298687760722947</v>
+        <v>0.9529446355643713</v>
       </c>
       <c r="AA4">
-        <v>0.1301268904641181</v>
+        <v>0.01558832250905089</v>
       </c>
       <c r="AB4">
-        <v>0.04157328756648297</v>
+        <v>0.06974039692155334</v>
       </c>
       <c r="AC4">
-        <v>0.08855360289763514</v>
+        <v>-0.05415207441250246</v>
       </c>
       <c r="AD4">
-        <v>42017.8</v>
+        <v>40129.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>42017.8</v>
+        <v>40129.4</v>
       </c>
       <c r="AG4">
-        <v>16593.6</v>
+        <v>13814.4</v>
       </c>
       <c r="AH4">
-        <v>0.3043649905433294</v>
+        <v>0.3174656166068723</v>
       </c>
       <c r="AI4">
-        <v>0.2980717254021199</v>
+        <v>0.4232625986581541</v>
       </c>
       <c r="AJ4">
-        <v>0.1473329988945764</v>
+        <v>0.1380190927210874</v>
       </c>
       <c r="AK4">
-        <v>0.14361630310227</v>
+        <v>0.2016856778699666</v>
       </c>
       <c r="AL4">
-        <v>1115</v>
+        <v>1472.8</v>
       </c>
       <c r="AM4">
-        <v>1115</v>
+        <v>1472.8</v>
       </c>
       <c r="AN4">
-        <v>2.12319415459401</v>
+        <v>10.5556461582976</v>
       </c>
       <c r="AO4">
-        <v>16.54744394618834</v>
+        <v>1.599877783813145</v>
       </c>
       <c r="AP4">
-        <v>0.8384883197994937</v>
+        <v>3.633742799274009</v>
       </c>
       <c r="AQ4">
-        <v>16.54744394618834</v>
+        <v>1.599877783813145</v>
       </c>
     </row>
     <row r="5">
@@ -993,22 +993,22 @@
         </is>
       </c>
       <c r="G5">
-        <v>-0.1118243243243243</v>
+        <v>0.01684782608695652</v>
       </c>
       <c r="H5">
-        <v>-0.1118243243243243</v>
+        <v>0.01684782608695652</v>
       </c>
       <c r="I5">
-        <v>-0.06193693693693694</v>
+        <v>0.02600931677018633</v>
       </c>
       <c r="J5">
-        <v>-0.06193693693693694</v>
+        <v>0.01300465838509317</v>
       </c>
       <c r="K5">
-        <v>-4.78</v>
+        <v>0.287</v>
       </c>
       <c r="L5">
-        <v>-0.05382882882882883</v>
+        <v>0.002228260869565217</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1017,7 +1017,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1026,37 +1026,37 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.36</v>
+        <v>7.6</v>
       </c>
       <c r="V5">
-        <v>0.007856730213749278</v>
+        <v>0.05667412378821775</v>
       </c>
       <c r="W5">
-        <v>-0.07220543806646526</v>
+        <v>0.002704995287464656</v>
       </c>
       <c r="X5">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="Y5">
-        <v>-0.1160227860339859</v>
+        <v>-0.07228887367041201</v>
       </c>
       <c r="Z5">
-        <v>1.372700571958572</v>
+        <v>1.229711666984915</v>
       </c>
       <c r="AA5">
-        <v>-0.08502086875869531</v>
+        <v>0.01599198014130227</v>
       </c>
       <c r="AB5">
-        <v>0.04381734796752063</v>
+        <v>0.07499386895787666</v>
       </c>
       <c r="AC5">
-        <v>-0.1288382167262159</v>
+        <v>-0.05900188881657438</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-1.36</v>
+        <v>-7.6</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1077,28 +1077,28 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.007918947245836732</v>
+        <v>-0.06007905138339921</v>
       </c>
       <c r="AK5">
-        <v>-0.01298453312965438</v>
+        <v>-0.112927191679049</v>
       </c>
       <c r="AL5">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AM5">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AN5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-4.867256637168142</v>
+        <v>2.537878787878788</v>
       </c>
       <c r="AP5">
-        <v>0.3090909090909091</v>
+        <v>-2.037533512064343</v>
       </c>
       <c r="AQ5">
-        <v>-4.867256637168142</v>
+        <v>2.537878787878788</v>
       </c>
     </row>
     <row r="6">
@@ -1118,46 +1118,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.133</v>
+        <v>-0.103</v>
       </c>
       <c r="E6">
-        <v>0.126</v>
+        <v>-0.108</v>
       </c>
       <c r="G6">
-        <v>-0.004404422522889422</v>
+        <v>-0.02860364978470371</v>
       </c>
       <c r="H6">
-        <v>-0.004404422522889422</v>
+        <v>-0.02860364978470371</v>
       </c>
       <c r="I6">
-        <v>-0.02776897898849118</v>
+        <v>-0.04651083316246327</v>
       </c>
       <c r="J6">
-        <v>-0.02776897898849118</v>
+        <v>-0.04002379590559339</v>
       </c>
       <c r="K6">
-        <v>85.7</v>
+        <v>41.5</v>
       </c>
       <c r="L6">
-        <v>0.01292667843190491</v>
+        <v>0.01418221584307293</v>
       </c>
       <c r="M6">
-        <v>45.1</v>
+        <v>39.7</v>
       </c>
       <c r="N6">
-        <v>0.0438715953307393</v>
+        <v>0.04328390754470127</v>
       </c>
       <c r="O6">
-        <v>0.5262543757292882</v>
+        <v>0.9566265060240965</v>
       </c>
       <c r="P6">
-        <v>45.1</v>
+        <v>39.7</v>
       </c>
       <c r="Q6">
-        <v>0.0438715953307393</v>
+        <v>0.04328390754470127</v>
       </c>
       <c r="R6">
-        <v>0.5262543757292882</v>
+        <v>0.9566265060240965</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1166,174 +1166,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>619.4</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.6753161796772786</v>
       </c>
       <c r="W6">
-        <v>0.08925223911685065</v>
+        <v>0.03931413414172035</v>
       </c>
       <c r="X6">
-        <v>0.0443648771700142</v>
+        <v>0.07562643297815005</v>
       </c>
       <c r="Y6">
-        <v>0.04488736194683645</v>
+        <v>-0.0363122988364297</v>
       </c>
       <c r="Z6">
-        <v>21.36338736184062</v>
+        <v>2.704211294809119</v>
       </c>
       <c r="AA6">
-        <v>-0.5932394547739502</v>
+        <v>-0.1082328009490406</v>
       </c>
       <c r="AB6">
-        <v>0.04362185373069513</v>
+        <v>0.07459077047926735</v>
       </c>
       <c r="AC6">
-        <v>-0.6368613085046454</v>
+        <v>-0.182823571428308</v>
       </c>
       <c r="AD6">
-        <v>28</v>
+        <v>22.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>28</v>
+        <v>22.9</v>
       </c>
       <c r="AG6">
-        <v>28</v>
+        <v>-596.5</v>
       </c>
       <c r="AH6">
-        <v>0.02651515151515152</v>
+        <v>0.02435911073290075</v>
       </c>
       <c r="AI6">
-        <v>0.02540143336659711</v>
+        <v>0.02354513674686408</v>
       </c>
       <c r="AJ6">
-        <v>0.02651515151515152</v>
+        <v>-1.859993763642033</v>
       </c>
       <c r="AK6">
-        <v>0.02540143336659711</v>
+        <v>-1.688844847112118</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="AN6">
-        <v>-0.07775617883921132</v>
+        <v>-0.2183031458531935</v>
+      </c>
+      <c r="AO6">
+        <v>-21.1993769470405</v>
       </c>
       <c r="AP6">
-        <v>-0.07775617883921132</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RheinLand Holding AG (DUSE:RLV)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0522</v>
-      </c>
-      <c r="E7">
-        <v>-0.0289</v>
-      </c>
-      <c r="G7">
-        <v>0.01263313124692774</v>
-      </c>
-      <c r="H7">
-        <v>0.01263313124692774</v>
-      </c>
-      <c r="I7">
-        <v>-0.003522857611010978</v>
-      </c>
-      <c r="J7">
-        <v>-0.002673800223656719</v>
-      </c>
-      <c r="K7">
-        <v>16.5</v>
-      </c>
-      <c r="L7">
-        <v>0.0270358839914796</v>
-      </c>
-      <c r="M7">
-        <v>5.64</v>
-      </c>
-      <c r="N7">
-        <v>0.03325471698113208</v>
-      </c>
-      <c r="O7">
-        <v>0.3418181818181818</v>
-      </c>
-      <c r="P7">
-        <v>5.64</v>
-      </c>
-      <c r="Q7">
-        <v>0.03325471698113208</v>
-      </c>
-      <c r="R7">
-        <v>0.3418181818181818</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0.04381734796752063</v>
-      </c>
-      <c r="AB7">
-        <v>0.04381734796752063</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
+        <v>5.686367969494756</v>
+      </c>
+      <c r="AQ6">
+        <v>-21.1993769470405</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00055</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.0915</v>
+        <v>0.01254</v>
       </c>
       <c r="F2">
-        <v>0.121</v>
+        <v>0.1073</v>
       </c>
       <c r="G2">
-        <v>0.08100394506062049</v>
+        <v>0.08504408211879165</v>
       </c>
       <c r="H2">
-        <v>0.08100394506062049</v>
+        <v>0.08504408211879165</v>
       </c>
       <c r="I2">
-        <v>0.03152437091240074</v>
+        <v>0.08520166626787229</v>
       </c>
       <c r="J2">
-        <v>0.02260177189187236</v>
+        <v>0.0738637456340991</v>
       </c>
       <c r="K2">
-        <v>5446.787</v>
+        <v>10399.97</v>
       </c>
       <c r="L2">
-        <v>0.03481514080005728</v>
+        <v>0.06174863128420306</v>
       </c>
       <c r="M2">
-        <v>39.7</v>
+        <v>595.989</v>
       </c>
       <c r="N2">
-        <v>0.0003996879011351338</v>
+        <v>0.004805223600210917</v>
       </c>
       <c r="O2">
-        <v>0.007288700659673309</v>
+        <v>0.05730679992346133</v>
       </c>
       <c r="P2">
-        <v>39.7</v>
+        <v>595.88</v>
       </c>
       <c r="Q2">
-        <v>0.0003996879011351338</v>
+        <v>0.004804344776319163</v>
       </c>
       <c r="R2">
-        <v>0.007288700659673309</v>
+        <v>0.05729631912399748</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.000182889281513585</v>
       </c>
       <c r="U2">
-        <v>26942</v>
+        <v>25562.2</v>
       </c>
       <c r="V2">
-        <v>0.2712441166847047</v>
+        <v>0.206097909044146</v>
       </c>
       <c r="W2">
-        <v>0.04265801188085191</v>
+        <v>0.1706466147699496</v>
       </c>
       <c r="X2">
-        <v>0.08120232024473512</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="Y2">
-        <v>-0.0385443083638832</v>
+        <v>0.1032127943934329</v>
       </c>
       <c r="Z2">
-        <v>1.245676624963583</v>
+        <v>2.585134032293243</v>
       </c>
       <c r="AA2">
-        <v>0.01579015132517658</v>
+        <v>-0.0193452380952381</v>
       </c>
       <c r="AB2">
-        <v>0.07231574267378031</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AC2">
-        <v>-0.05657698161453842</v>
+        <v>-0.08677905847175488</v>
       </c>
       <c r="AD2">
-        <v>46804.6</v>
+        <v>16.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>46804.6</v>
+        <v>16.1</v>
       </c>
       <c r="AG2">
-        <v>19862.6</v>
+        <v>-25546.1</v>
       </c>
       <c r="AH2">
-        <v>0.3202896557293025</v>
+        <v>0.0001297910847229444</v>
       </c>
       <c r="AI2">
-        <v>0.4031970035414101</v>
+        <v>0.0001958313466385124</v>
       </c>
       <c r="AJ2">
-        <v>0.1666463909334752</v>
+        <v>-0.2593952477222027</v>
       </c>
       <c r="AK2">
-        <v>0.2228205205868858</v>
+        <v>-0.4509350166103575</v>
       </c>
       <c r="AL2">
-        <v>1691.34</v>
+        <v>1576.42</v>
       </c>
       <c r="AM2">
-        <v>1691.34</v>
+        <v>1576.42</v>
       </c>
       <c r="AN2">
-        <v>6.953040393491524</v>
+        <v>0.0009912884829271801</v>
       </c>
       <c r="AO2">
-        <v>2.916001513592773</v>
+        <v>9.102923713223635</v>
       </c>
       <c r="AP2">
-        <v>2.950681345845595</v>
+        <v>-1.572891597124598</v>
       </c>
       <c r="AQ2">
-        <v>2.916001513592773</v>
+        <v>9.102923713223635</v>
       </c>
     </row>
     <row r="3">
@@ -725,121 +725,109 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0868</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="E3">
-        <v>0.0858</v>
+        <v>0.164</v>
       </c>
       <c r="F3">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
       <c r="G3">
-        <v>0.0711707968353536</v>
+        <v>0.06661351129460637</v>
       </c>
       <c r="H3">
-        <v>0.0711707968353536</v>
+        <v>0.06661351129460637</v>
       </c>
       <c r="I3">
-        <v>0.05712562195088512</v>
+        <v>0.07032710578101078</v>
       </c>
       <c r="J3">
-        <v>0.04407599674368774</v>
+        <v>0.05475160901909285</v>
       </c>
       <c r="K3">
-        <v>1052.2</v>
+        <v>1614.1</v>
       </c>
       <c r="L3">
-        <v>0.02219302149487569</v>
+        <v>0.02938290617894792</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>546.96</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02966353558799922</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3388637630877889</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>546.96</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02966353558799922</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3388637630877889</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
         <v>0</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
-      <c r="W3">
-        <v>0.08523495913225919</v>
-      </c>
       <c r="X3">
-        <v>0.0890388129273384</v>
-      </c>
-      <c r="Y3">
-        <v>-0.003803853795079207</v>
-      </c>
-      <c r="Z3">
-        <v>3.594270248961398</v>
-      </c>
-      <c r="AA3">
-        <v>0.1584210437891563</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AB3">
-        <v>0.07004071486829327</v>
-      </c>
-      <c r="AC3">
-        <v>0.08838032892086303</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AD3">
-        <v>6652.3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6652.3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>6652.3</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.3566457935708005</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.3288903171581836</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.3566457935708005</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>0.3288903171581836</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>210.8</v>
+        <v>313.3</v>
       </c>
       <c r="AM3">
-        <v>210.8</v>
+        <v>313.3</v>
       </c>
       <c r="AN3">
-        <v>2.194754206532497</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>12.84819734345351</v>
+        <v>12.33099265879349</v>
       </c>
       <c r="AP3">
-        <v>2.194754206532497</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>12.84819734345351</v>
+        <v>12.33099265879349</v>
       </c>
     </row>
     <row r="4">
@@ -859,31 +847,31 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00055</v>
+        <v>-0.009689999999999999</v>
       </c>
       <c r="E4">
-        <v>-0.0915</v>
+        <v>0.0269</v>
       </c>
       <c r="F4">
-        <v>0.104</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="G4">
-        <v>0.08850706484561131</v>
+        <v>0.09936237700373651</v>
       </c>
       <c r="H4">
-        <v>0.08850706484561131</v>
+        <v>0.09936237700373651</v>
       </c>
       <c r="I4">
-        <v>0.02223291581157267</v>
+        <v>0.097837042850968</v>
       </c>
       <c r="J4">
-        <v>0.01635805683487464</v>
+        <v>0.07617731611113959</v>
       </c>
       <c r="K4">
-        <v>4352.8</v>
+        <v>8691.799999999999</v>
       </c>
       <c r="L4">
-        <v>0.04107093152171349</v>
+        <v>0.08044841862277505</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -907,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>26315</v>
+        <v>25551.4</v>
       </c>
       <c r="V4">
-        <v>0.3050091508540604</v>
+        <v>0.2445840289158103</v>
       </c>
       <c r="W4">
-        <v>0.04600188961998347</v>
+        <v>0.1706466147699496</v>
       </c>
       <c r="X4">
-        <v>0.08677820751132019</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="Y4">
-        <v>-0.04077631789133672</v>
+        <v>0.1032127943934329</v>
       </c>
       <c r="Z4">
-        <v>0.9529446355643713</v>
+        <v>1.668629119568054</v>
       </c>
       <c r="AA4">
-        <v>0.01558832250905089</v>
+        <v>0.1271116879135883</v>
       </c>
       <c r="AB4">
-        <v>0.06974039692155334</v>
+        <v>0.06743382037651678</v>
       </c>
       <c r="AC4">
-        <v>-0.05415207441250246</v>
+        <v>0.05967786753707148</v>
       </c>
       <c r="AD4">
-        <v>40129.4</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>40129.4</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>13814.4</v>
+        <v>-25551.4</v>
       </c>
       <c r="AH4">
-        <v>0.3174656166068723</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.4232625986581541</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.1380190927210874</v>
+        <v>-0.3237739712661594</v>
       </c>
       <c r="AK4">
-        <v>0.2016856778699666</v>
+        <v>-0.6605262205493829</v>
       </c>
       <c r="AL4">
-        <v>1472.8</v>
+        <v>1261.6</v>
       </c>
       <c r="AM4">
-        <v>1472.8</v>
+        <v>1261.6</v>
       </c>
       <c r="AN4">
-        <v>10.5556461582976</v>
+        <v>0</v>
       </c>
       <c r="AO4">
-        <v>1.599877783813145</v>
+        <v>8.378646163601775</v>
       </c>
       <c r="AP4">
-        <v>3.633742799274009</v>
+        <v>-2.111563793830109</v>
       </c>
       <c r="AQ4">
-        <v>1.599877783813145</v>
+        <v>8.378646163601775</v>
       </c>
     </row>
     <row r="5">
@@ -992,32 +980,35 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.289</v>
+      </c>
       <c r="G5">
-        <v>0.01684782608695652</v>
+        <v>0.03328209069946195</v>
       </c>
       <c r="H5">
-        <v>0.01684782608695652</v>
+        <v>0.03328209069946195</v>
       </c>
       <c r="I5">
-        <v>0.02600931677018633</v>
+        <v>-0.009992313604919294</v>
       </c>
       <c r="J5">
-        <v>0.01300465838509317</v>
+        <v>-0.009992313604919294</v>
       </c>
       <c r="K5">
-        <v>0.287</v>
+        <v>-1.83</v>
       </c>
       <c r="L5">
-        <v>0.002228260869565217</v>
+        <v>-0.01406610299769408</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.109</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.001014897579143389</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>-0.05956284153005464</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1026,79 +1017,82 @@
         <v>-0</v>
       </c>
       <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0.109</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>10.8</v>
+      </c>
+      <c r="V5">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="W5">
+        <v>-0.02446524064171123</v>
+      </c>
+      <c r="X5">
+        <v>0.06743382037651678</v>
+      </c>
+      <c r="Y5">
+        <v>-0.09189906101822801</v>
+      </c>
+      <c r="Z5">
+        <v>1.936011904761905</v>
+      </c>
+      <c r="AA5">
+        <v>-0.0193452380952381</v>
+      </c>
+      <c r="AB5">
+        <v>0.06743382037651678</v>
+      </c>
+      <c r="AC5">
+        <v>-0.08677905847175488</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-10.8</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1118012422360248</v>
+      </c>
+      <c r="AK5">
+        <v>-0.1198668146503885</v>
+      </c>
+      <c r="AL5">
+        <v>1.52</v>
+      </c>
+      <c r="AM5">
+        <v>1.52</v>
+      </c>
+      <c r="AN5">
         <v>-0</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>7.6</v>
-      </c>
-      <c r="V5">
-        <v>0.05667412378821775</v>
-      </c>
-      <c r="W5">
-        <v>0.002704995287464656</v>
-      </c>
-      <c r="X5">
-        <v>0.07499386895787666</v>
-      </c>
-      <c r="Y5">
-        <v>-0.07228887367041201</v>
-      </c>
-      <c r="Z5">
-        <v>1.229711666984915</v>
-      </c>
-      <c r="AA5">
-        <v>0.01599198014130227</v>
-      </c>
-      <c r="AB5">
-        <v>0.07499386895787666</v>
-      </c>
-      <c r="AC5">
-        <v>-0.05900188881657438</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>-7.6</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.06007905138339921</v>
-      </c>
-      <c r="AK5">
-        <v>-0.112927191679049</v>
-      </c>
-      <c r="AL5">
-        <v>1.32</v>
-      </c>
-      <c r="AM5">
-        <v>1.32</v>
-      </c>
-      <c r="AN5">
-        <v>0</v>
-      </c>
       <c r="AO5">
-        <v>2.537878787878788</v>
+        <v>-0.8552631578947368</v>
       </c>
       <c r="AP5">
-        <v>-2.037533512064343</v>
+        <v>39.70588235294117</v>
       </c>
       <c r="AQ5">
-        <v>2.537878787878788</v>
+        <v>-0.8552631578947368</v>
       </c>
     </row>
     <row r="6">
@@ -1118,46 +1112,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.103</v>
+        <v>0.0104</v>
       </c>
       <c r="E6">
-        <v>-0.108</v>
+        <v>-0.00182</v>
       </c>
       <c r="G6">
-        <v>-0.02860364978470371</v>
+        <v>-0.01793960545636398</v>
       </c>
       <c r="H6">
-        <v>-0.02860364978470371</v>
+        <v>-0.01793960545636398</v>
       </c>
       <c r="I6">
-        <v>-0.04651083316246327</v>
+        <v>-0.01740758868719542</v>
       </c>
       <c r="J6">
-        <v>-0.04002379590559339</v>
+        <v>-0.01740758868719542</v>
       </c>
       <c r="K6">
-        <v>41.5</v>
+        <v>83.5</v>
       </c>
       <c r="L6">
-        <v>0.01418221584307293</v>
+        <v>0.01776936009023004</v>
       </c>
       <c r="M6">
-        <v>39.7</v>
+        <v>44</v>
       </c>
       <c r="N6">
-        <v>0.04328390754470127</v>
+        <v>0.05157660297737662</v>
       </c>
       <c r="O6">
-        <v>0.9566265060240965</v>
+        <v>0.5269461077844312</v>
       </c>
       <c r="P6">
-        <v>39.7</v>
+        <v>44</v>
       </c>
       <c r="Q6">
-        <v>0.04328390754470127</v>
+        <v>0.05157660297737662</v>
       </c>
       <c r="R6">
-        <v>0.9566265060240965</v>
+        <v>0.5269461077844312</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1166,73 +1160,174 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>619.4</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.6753161796772786</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.03931413414172035</v>
+        <v>0.08953463435556508</v>
       </c>
       <c r="X6">
-        <v>0.07562643297815005</v>
+        <v>0.06781209157056595</v>
       </c>
       <c r="Y6">
-        <v>-0.0363122988364297</v>
+        <v>0.02172254278499913</v>
       </c>
       <c r="Z6">
-        <v>2.704211294809119</v>
+        <v>14.02758291292277</v>
       </c>
       <c r="AA6">
-        <v>-0.1082328009490406</v>
+        <v>-0.2441863936236902</v>
       </c>
       <c r="AB6">
-        <v>0.07459077047926735</v>
+        <v>0.06714004823843743</v>
       </c>
       <c r="AC6">
-        <v>-0.182823571428308</v>
+        <v>-0.3113264418621277</v>
       </c>
       <c r="AD6">
-        <v>22.9</v>
+        <v>16.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>22.9</v>
+        <v>16.1</v>
       </c>
       <c r="AG6">
-        <v>-596.5</v>
+        <v>16.1</v>
       </c>
       <c r="AH6">
-        <v>0.02435911073290075</v>
+        <v>0.01852277956741832</v>
       </c>
       <c r="AI6">
-        <v>0.02354513674686408</v>
+        <v>0.01534941367146535</v>
       </c>
       <c r="AJ6">
-        <v>-1.859993763642033</v>
+        <v>0.01852277956741832</v>
       </c>
       <c r="AK6">
-        <v>-1.688844847112118</v>
+        <v>0.01534941367146535</v>
       </c>
       <c r="AL6">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>-0.2183031458531935</v>
-      </c>
-      <c r="AO6">
-        <v>-21.1993769470405</v>
+        <v>-0.3049242424242425</v>
       </c>
       <c r="AP6">
-        <v>5.686367969494756</v>
-      </c>
-      <c r="AQ6">
-        <v>-21.1993769470405</v>
+        <v>-0.3049242424242425</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RheinLand Holding AG (DUSE:RLV)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.05429999999999999</v>
+      </c>
+      <c r="E7">
+        <v>-0.0319</v>
+      </c>
+      <c r="G7">
+        <v>0.01429262784320052</v>
+      </c>
+      <c r="H7">
+        <v>0.01429262784320052</v>
+      </c>
+      <c r="I7">
+        <v>-0.001079206323600581</v>
+      </c>
+      <c r="J7">
+        <v>-0.0008390829165994516</v>
+      </c>
+      <c r="K7">
+        <v>12.4</v>
+      </c>
+      <c r="L7">
+        <v>0.02000322632682691</v>
+      </c>
+      <c r="M7">
+        <v>4.92</v>
+      </c>
+      <c r="N7">
+        <v>0.03050216986980781</v>
+      </c>
+      <c r="O7">
+        <v>0.3967741935483871</v>
+      </c>
+      <c r="P7">
+        <v>4.92</v>
+      </c>
+      <c r="Q7">
+        <v>0.03050216986980781</v>
+      </c>
+      <c r="R7">
+        <v>0.3967741935483871</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.06743382037651678</v>
+      </c>
+      <c r="AB7">
+        <v>0.06743382037651678</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05429999999999999</v>
+        <v>0.019</v>
       </c>
       <c r="E2">
-        <v>0.01254</v>
+        <v>0.09494999999999999</v>
       </c>
       <c r="F2">
-        <v>0.1073</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.08504408211879165</v>
+        <v>0.116542657253369</v>
       </c>
       <c r="H2">
-        <v>0.08504408211879165</v>
+        <v>0.116542657253369</v>
       </c>
       <c r="I2">
-        <v>0.08520166626787229</v>
+        <v>0.1254141235068688</v>
       </c>
       <c r="J2">
-        <v>0.0738637456340991</v>
+        <v>0.09961304775690409</v>
       </c>
       <c r="K2">
-        <v>10399.97</v>
+        <v>12830.7</v>
       </c>
       <c r="L2">
-        <v>0.06174863128420306</v>
+        <v>0.07876219350870418</v>
       </c>
       <c r="M2">
-        <v>595.989</v>
+        <v>675.698</v>
       </c>
       <c r="N2">
-        <v>0.004805223600210917</v>
+        <v>0.004820835889898832</v>
       </c>
       <c r="O2">
-        <v>0.05730679992346133</v>
+        <v>0.05266259829939131</v>
       </c>
       <c r="P2">
-        <v>595.88</v>
+        <v>675.698</v>
       </c>
       <c r="Q2">
-        <v>0.004804344776319163</v>
+        <v>0.004820835889898832</v>
       </c>
       <c r="R2">
-        <v>0.05729631912399748</v>
+        <v>0.05266259829939131</v>
       </c>
       <c r="S2">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.000182889281513585</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>25562.2</v>
+        <v>34527.1</v>
       </c>
       <c r="V2">
-        <v>0.206097909044146</v>
+        <v>0.2463370956464662</v>
       </c>
       <c r="W2">
-        <v>0.1706466147699496</v>
+        <v>0.1910708836452728</v>
       </c>
       <c r="X2">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
       </c>
       <c r="Y2">
-        <v>0.1032127943934329</v>
+        <v>0.1183004044097976</v>
       </c>
       <c r="Z2">
-        <v>2.585134032293243</v>
+        <v>3.677879123112004</v>
       </c>
       <c r="AA2">
-        <v>-0.0193452380952381</v>
+        <v>0.3769808952793049</v>
       </c>
       <c r="AB2">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
       </c>
       <c r="AC2">
-        <v>-0.08677905847175488</v>
+        <v>0.3042104160438297</v>
       </c>
       <c r="AD2">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>-25546.1</v>
+        <v>-34527.1</v>
       </c>
       <c r="AH2">
-        <v>0.0001297910847229444</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.0001958313466385124</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2593952477222027</v>
+        <v>-0.3268531517519305</v>
       </c>
       <c r="AK2">
-        <v>-0.4509350166103575</v>
+        <v>-0.6354065066085617</v>
       </c>
       <c r="AL2">
-        <v>1576.42</v>
+        <v>399.3</v>
       </c>
       <c r="AM2">
-        <v>1576.42</v>
+        <v>246.5</v>
       </c>
       <c r="AN2">
-        <v>0.0009912884829271801</v>
+        <v>0</v>
       </c>
       <c r="AO2">
-        <v>9.102923713223635</v>
+        <v>51.16579013273228</v>
       </c>
       <c r="AP2">
-        <v>-1.572891597124598</v>
+        <v>-1.57012733060482</v>
       </c>
       <c r="AQ2">
-        <v>9.102923713223635</v>
+        <v>82.88235294117646</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08380000000000001</v>
+        <v>0.0571</v>
       </c>
       <c r="E3">
-        <v>0.164</v>
+        <v>0.146</v>
       </c>
       <c r="F3">
-        <v>0.131</v>
+        <v>0.126</v>
       </c>
       <c r="G3">
-        <v>0.06661351129460637</v>
+        <v>0.08257457233890035</v>
       </c>
       <c r="H3">
-        <v>0.06661351129460637</v>
+        <v>0.08257457233890035</v>
       </c>
       <c r="I3">
-        <v>0.07032710578101078</v>
+        <v>0.09600284523855593</v>
       </c>
       <c r="J3">
-        <v>0.05475160901909285</v>
+        <v>0.07939256368402449</v>
       </c>
       <c r="K3">
-        <v>1614.1</v>
+        <v>2112.4</v>
       </c>
       <c r="L3">
-        <v>0.02938290617894792</v>
+        <v>0.03892669640899199</v>
       </c>
       <c r="M3">
-        <v>546.96</v>
+        <v>675.698</v>
       </c>
       <c r="N3">
-        <v>0.02966353558799922</v>
+        <v>0.03080469936038003</v>
       </c>
       <c r="O3">
-        <v>0.3388637630877889</v>
+        <v>0.3198721832986177</v>
       </c>
       <c r="P3">
-        <v>546.96</v>
+        <v>675.698</v>
       </c>
       <c r="Q3">
-        <v>0.02966353558799922</v>
+        <v>0.03080469936038003</v>
       </c>
       <c r="R3">
-        <v>0.3388637630877889</v>
+        <v>0.3198721832986177</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -781,11 +781,26 @@
       <c r="V3">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>0.2015956634600703</v>
+      </c>
       <c r="X3">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
+      </c>
+      <c r="Y3">
+        <v>0.128825184224595</v>
+      </c>
+      <c r="Z3">
+        <v>5.178853641777371</v>
+      </c>
+      <c r="AA3">
+        <v>0.4111624675650521</v>
       </c>
       <c r="AB3">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
+      </c>
+      <c r="AC3">
+        <v>0.3383919883295768</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -812,22 +827,22 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>313.3</v>
+        <v>399.3</v>
       </c>
       <c r="AM3">
-        <v>313.3</v>
+        <v>399.3</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>12.33099265879349</v>
+        <v>13.04708239418983</v>
       </c>
       <c r="AP3">
         <v>0</v>
       </c>
       <c r="AQ3">
-        <v>12.33099265879349</v>
+        <v>13.04708239418983</v>
       </c>
     </row>
     <row r="4">
@@ -847,31 +862,31 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.009689999999999999</v>
+        <v>-0.0191</v>
       </c>
       <c r="E4">
-        <v>0.0269</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F4">
-        <v>0.08359999999999999</v>
+        <v>0.078</v>
       </c>
       <c r="G4">
-        <v>0.09936237700373651</v>
+        <v>0.1335101281133156</v>
       </c>
       <c r="H4">
-        <v>0.09936237700373651</v>
+        <v>0.1335101281133156</v>
       </c>
       <c r="I4">
-        <v>0.097837042850968</v>
+        <v>0.140105414117686</v>
       </c>
       <c r="J4">
-        <v>0.07617731611113959</v>
+        <v>0.1066993192753374</v>
       </c>
       <c r="K4">
-        <v>8691.799999999999</v>
+        <v>10718.3</v>
       </c>
       <c r="L4">
-        <v>0.08044841862277505</v>
+        <v>0.09866050799810748</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,31 +910,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>25551.4</v>
+        <v>34527.1</v>
       </c>
       <c r="V4">
-        <v>0.2445840289158103</v>
+        <v>0.2920404881791061</v>
       </c>
       <c r="W4">
-        <v>0.1706466147699496</v>
+        <v>0.1805461038304753</v>
       </c>
       <c r="X4">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
       </c>
       <c r="Y4">
-        <v>0.1032127943934329</v>
+        <v>0.1077756245950001</v>
       </c>
       <c r="Z4">
-        <v>1.668629119568054</v>
+        <v>3.212760168684533</v>
       </c>
       <c r="AA4">
-        <v>0.1271116879135883</v>
+        <v>0.3427993229935578</v>
       </c>
       <c r="AB4">
-        <v>0.06743382037651678</v>
+        <v>0.07277047923547522</v>
       </c>
       <c r="AC4">
-        <v>0.05967786753707148</v>
+        <v>0.2700288437580826</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -931,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-25551.4</v>
+        <v>-34527.1</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -940,394 +955,25 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.3237739712661594</v>
+        <v>-0.4125101553166069</v>
       </c>
       <c r="AK4">
-        <v>-0.6605262205493829</v>
+        <v>-1.017651982716442</v>
       </c>
       <c r="AL4">
-        <v>1261.6</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>1261.6</v>
+        <v>-152.8</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
-      <c r="AO4">
-        <v>8.378646163601775</v>
-      </c>
       <c r="AP4">
-        <v>-2.111563793830109</v>
+        <v>-2.09693601773405</v>
       </c>
       <c r="AQ4">
-        <v>8.378646163601775</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DFV Deutsche Familienversicherung AG (XTRA:DFV)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.289</v>
-      </c>
-      <c r="G5">
-        <v>0.03328209069946195</v>
-      </c>
-      <c r="H5">
-        <v>0.03328209069946195</v>
-      </c>
-      <c r="I5">
-        <v>-0.009992313604919294</v>
-      </c>
-      <c r="J5">
-        <v>-0.009992313604919294</v>
-      </c>
-      <c r="K5">
-        <v>-1.83</v>
-      </c>
-      <c r="L5">
-        <v>-0.01406610299769408</v>
-      </c>
-      <c r="M5">
-        <v>0.109</v>
-      </c>
-      <c r="N5">
-        <v>0.001014897579143389</v>
-      </c>
-      <c r="O5">
-        <v>-0.05956284153005464</v>
-      </c>
-      <c r="P5">
-        <v>-0</v>
-      </c>
-      <c r="Q5">
-        <v>-0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0.109</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>10.8</v>
-      </c>
-      <c r="V5">
-        <v>0.1005586592178771</v>
-      </c>
-      <c r="W5">
-        <v>-0.02446524064171123</v>
-      </c>
-      <c r="X5">
-        <v>0.06743382037651678</v>
-      </c>
-      <c r="Y5">
-        <v>-0.09189906101822801</v>
-      </c>
-      <c r="Z5">
-        <v>1.936011904761905</v>
-      </c>
-      <c r="AA5">
-        <v>-0.0193452380952381</v>
-      </c>
-      <c r="AB5">
-        <v>0.06743382037651678</v>
-      </c>
-      <c r="AC5">
-        <v>-0.08677905847175488</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>-10.8</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.1118012422360248</v>
-      </c>
-      <c r="AK5">
-        <v>-0.1198668146503885</v>
-      </c>
-      <c r="AL5">
-        <v>1.52</v>
-      </c>
-      <c r="AM5">
-        <v>1.52</v>
-      </c>
-      <c r="AN5">
-        <v>-0</v>
-      </c>
-      <c r="AO5">
-        <v>-0.8552631578947368</v>
-      </c>
-      <c r="AP5">
-        <v>39.70588235294117</v>
-      </c>
-      <c r="AQ5">
-        <v>-0.8552631578947368</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NÜRNBERGER Beteiligungs-AG (XTRA:NBG6)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0104</v>
-      </c>
-      <c r="E6">
-        <v>-0.00182</v>
-      </c>
-      <c r="G6">
-        <v>-0.01793960545636398</v>
-      </c>
-      <c r="H6">
-        <v>-0.01793960545636398</v>
-      </c>
-      <c r="I6">
-        <v>-0.01740758868719542</v>
-      </c>
-      <c r="J6">
-        <v>-0.01740758868719542</v>
-      </c>
-      <c r="K6">
-        <v>83.5</v>
-      </c>
-      <c r="L6">
-        <v>0.01776936009023004</v>
-      </c>
-      <c r="M6">
-        <v>44</v>
-      </c>
-      <c r="N6">
-        <v>0.05157660297737662</v>
-      </c>
-      <c r="O6">
-        <v>0.5269461077844312</v>
-      </c>
-      <c r="P6">
-        <v>44</v>
-      </c>
-      <c r="Q6">
-        <v>0.05157660297737662</v>
-      </c>
-      <c r="R6">
-        <v>0.5269461077844312</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0.08953463435556508</v>
-      </c>
-      <c r="X6">
-        <v>0.06781209157056595</v>
-      </c>
-      <c r="Y6">
-        <v>0.02172254278499913</v>
-      </c>
-      <c r="Z6">
-        <v>14.02758291292277</v>
-      </c>
-      <c r="AA6">
-        <v>-0.2441863936236902</v>
-      </c>
-      <c r="AB6">
-        <v>0.06714004823843743</v>
-      </c>
-      <c r="AC6">
-        <v>-0.3113264418621277</v>
-      </c>
-      <c r="AD6">
-        <v>16.1</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>16.1</v>
-      </c>
-      <c r="AG6">
-        <v>16.1</v>
-      </c>
-      <c r="AH6">
-        <v>0.01852277956741832</v>
-      </c>
-      <c r="AI6">
-        <v>0.01534941367146535</v>
-      </c>
-      <c r="AJ6">
-        <v>0.01852277956741832</v>
-      </c>
-      <c r="AK6">
-        <v>0.01534941367146535</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>-0.3049242424242425</v>
-      </c>
-      <c r="AP6">
-        <v>-0.3049242424242425</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RheinLand Holding AG (DUSE:RLV)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.05429999999999999</v>
-      </c>
-      <c r="E7">
-        <v>-0.0319</v>
-      </c>
-      <c r="G7">
-        <v>0.01429262784320052</v>
-      </c>
-      <c r="H7">
-        <v>0.01429262784320052</v>
-      </c>
-      <c r="I7">
-        <v>-0.001079206323600581</v>
-      </c>
-      <c r="J7">
-        <v>-0.0008390829165994516</v>
-      </c>
-      <c r="K7">
-        <v>12.4</v>
-      </c>
-      <c r="L7">
-        <v>0.02000322632682691</v>
-      </c>
-      <c r="M7">
-        <v>4.92</v>
-      </c>
-      <c r="N7">
-        <v>0.03050216986980781</v>
-      </c>
-      <c r="O7">
-        <v>0.3967741935483871</v>
-      </c>
-      <c r="P7">
-        <v>4.92</v>
-      </c>
-      <c r="Q7">
-        <v>0.03050216986980781</v>
-      </c>
-      <c r="R7">
-        <v>0.3967741935483871</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0.06743382037651678</v>
-      </c>
-      <c r="AB7">
-        <v>0.06743382037651678</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
+        <v>-99.61256544502616</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.019</v>
+        <v>0.09005000000000001</v>
       </c>
       <c r="E2">
-        <v>0.09494999999999999</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="F2">
         <v>0.102</v>
       </c>
       <c r="G2">
-        <v>0.116542657253369</v>
+        <v>0.1125821945307737</v>
       </c>
       <c r="H2">
-        <v>0.116542657253369</v>
+        <v>0.1125821945307737</v>
       </c>
       <c r="I2">
-        <v>0.1254141235068688</v>
+        <v>0.1209465716962334</v>
       </c>
       <c r="J2">
-        <v>0.09961304775690409</v>
+        <v>0.09152716252511676</v>
       </c>
       <c r="K2">
-        <v>12830.7</v>
+        <v>12881.42</v>
       </c>
       <c r="L2">
-        <v>0.07876219350870418</v>
+        <v>0.07661925084387872</v>
       </c>
       <c r="M2">
-        <v>675.698</v>
+        <v>720.298</v>
       </c>
       <c r="N2">
-        <v>0.004820835889898832</v>
+        <v>0.005115124349067905</v>
       </c>
       <c r="O2">
-        <v>0.05266259829939131</v>
+        <v>0.0559175929361825</v>
       </c>
       <c r="P2">
-        <v>675.698</v>
+        <v>720.298</v>
       </c>
       <c r="Q2">
-        <v>0.004820835889898832</v>
+        <v>0.005115124349067905</v>
       </c>
       <c r="R2">
-        <v>0.05266259829939131</v>
+        <v>0.0559175929361825</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>34527.1</v>
+        <v>35141</v>
       </c>
       <c r="V2">
-        <v>0.2463370956464662</v>
+        <v>0.2495503038334068</v>
       </c>
       <c r="W2">
-        <v>0.1910708836452728</v>
+        <v>0.1131897185819043</v>
       </c>
       <c r="X2">
-        <v>0.07277047923547522</v>
+        <v>0.07303397072471823</v>
       </c>
       <c r="Y2">
-        <v>0.1183004044097976</v>
+        <v>0.04015574785718611</v>
       </c>
       <c r="Z2">
-        <v>3.677879123112004</v>
+        <v>3.759575459631007</v>
       </c>
       <c r="AA2">
-        <v>0.3769808952793049</v>
+        <v>0.2109788304515656</v>
       </c>
       <c r="AB2">
-        <v>0.07277047923547522</v>
+        <v>0.07249836847446409</v>
       </c>
       <c r="AC2">
-        <v>0.3042104160438297</v>
+        <v>0.1388787251076646</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>26.34</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>26.34</v>
       </c>
       <c r="AG2">
-        <v>-34527.1</v>
+        <v>-35114.66</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.0001870158993334736</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.0002924205785042676</v>
       </c>
       <c r="AJ2">
-        <v>-0.3268531517519305</v>
+        <v>-0.3322022988262166</v>
       </c>
       <c r="AK2">
-        <v>-0.6354065066085617</v>
+        <v>-0.6392068115731503</v>
       </c>
       <c r="AL2">
         <v>399.3</v>
@@ -696,16 +696,16 @@
         <v>246.5</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.001200952007513929</v>
       </c>
       <c r="AO2">
-        <v>51.16579013273228</v>
+        <v>50.92371650388179</v>
       </c>
       <c r="AP2">
-        <v>-1.57012733060482</v>
+        <v>-1.601025870165872</v>
       </c>
       <c r="AQ2">
-        <v>82.88235294117646</v>
+        <v>82.49022312373225</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>0.2015956634600703</v>
       </c>
       <c r="X3">
-        <v>0.07277047923547522</v>
+        <v>0.07275313961528646</v>
       </c>
       <c r="Y3">
-        <v>0.128825184224595</v>
+        <v>0.1288425238447838</v>
       </c>
       <c r="Z3">
         <v>5.178853641777371</v>
@@ -797,10 +797,10 @@
         <v>0.4111624675650521</v>
       </c>
       <c r="AB3">
-        <v>0.07277047923547522</v>
+        <v>0.07275313961528646</v>
       </c>
       <c r="AC3">
-        <v>0.3383919883295768</v>
+        <v>0.3384093279497656</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -919,10 +919,10 @@
         <v>0.1805461038304753</v>
       </c>
       <c r="X4">
-        <v>0.07277047923547522</v>
+        <v>0.07275313961528646</v>
       </c>
       <c r="Y4">
-        <v>0.1077756245950001</v>
+        <v>0.1077929642151889</v>
       </c>
       <c r="Z4">
         <v>3.212760168684533</v>
@@ -931,10 +931,10 @@
         <v>0.3427993229935578</v>
       </c>
       <c r="AB4">
-        <v>0.07277047923547522</v>
+        <v>0.07275313961528646</v>
       </c>
       <c r="AC4">
-        <v>0.2700288437580826</v>
+        <v>0.2700461833782713</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -974,6 +974,256 @@
       </c>
       <c r="AQ4">
         <v>-99.61256544502616</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DFV Deutsche Familienversicherung AG (HMSE:DFV)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.232</v>
+      </c>
+      <c r="G5">
+        <v>0.07158509861212564</v>
+      </c>
+      <c r="H5">
+        <v>0.07158509861212564</v>
+      </c>
+      <c r="I5">
+        <v>0.06822498173849526</v>
+      </c>
+      <c r="J5">
+        <v>0.05203981308883576</v>
+      </c>
+      <c r="K5">
+        <v>4.62</v>
+      </c>
+      <c r="L5">
+        <v>0.0337472607742878</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>19.6</v>
+      </c>
+      <c r="V5">
+        <v>0.223744292237443</v>
+      </c>
+      <c r="W5">
+        <v>0.04583333333333334</v>
+      </c>
+      <c r="X5">
+        <v>0.0747863170876359</v>
+      </c>
+      <c r="Y5">
+        <v>-0.02895298375430257</v>
+      </c>
+      <c r="Z5">
+        <v>1.521111111111111</v>
+      </c>
+      <c r="AA5">
+        <v>0.0791583379095735</v>
+      </c>
+      <c r="AB5">
+        <v>0.07144707107251551</v>
+      </c>
+      <c r="AC5">
+        <v>0.007711266837057987</v>
+      </c>
+      <c r="AD5">
+        <v>9.44</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>9.44</v>
+      </c>
+      <c r="AG5">
+        <v>-10.16</v>
+      </c>
+      <c r="AH5">
+        <v>0.09727947238252267</v>
+      </c>
+      <c r="AI5">
+        <v>0.07567740901074234</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1311983471074381</v>
+      </c>
+      <c r="AK5">
+        <v>-0.09663306068099678</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0.9346534653465346</v>
+      </c>
+      <c r="AP5">
+        <v>-1.005940594059406</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NÜRNBERGER Beteiligungs-AG (XTRA:NBG6)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.123</v>
+      </c>
+      <c r="E6">
+        <v>-0.0663</v>
+      </c>
+      <c r="G6">
+        <v>-0.01328400212544034</v>
+      </c>
+      <c r="H6">
+        <v>-0.01328400212544034</v>
+      </c>
+      <c r="I6">
+        <v>-0.02086080333772853</v>
+      </c>
+      <c r="J6">
+        <v>-0.01409594282677942</v>
+      </c>
+      <c r="K6">
+        <v>46.1</v>
+      </c>
+      <c r="L6">
+        <v>0.009072481451597033</v>
+      </c>
+      <c r="M6">
+        <v>44.6</v>
+      </c>
+      <c r="N6">
+        <v>0.07856262110269509</v>
+      </c>
+      <c r="O6">
+        <v>0.9674620390455532</v>
+      </c>
+      <c r="P6">
+        <v>44.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.07856262110269509</v>
+      </c>
+      <c r="R6">
+        <v>0.9674620390455532</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>594.3</v>
+      </c>
+      <c r="V6">
+        <v>1.046855733662145</v>
+      </c>
+      <c r="W6">
+        <v>0.04546799487128909</v>
+      </c>
+      <c r="X6">
+        <v>0.07331480183415</v>
+      </c>
+      <c r="Y6">
+        <v>-0.02784680696286091</v>
+      </c>
+      <c r="Z6">
+        <v>15.14635745797067</v>
+      </c>
+      <c r="AA6">
+        <v>-0.2135021887615187</v>
+      </c>
+      <c r="AB6">
+        <v>0.07224359733364173</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2857457860951604</v>
+      </c>
+      <c r="AD6">
+        <v>16.9</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>16.9</v>
+      </c>
+      <c r="AG6">
+        <v>-577.4</v>
+      </c>
+      <c r="AH6">
+        <v>0.02890865549093397</v>
+      </c>
+      <c r="AI6">
+        <v>0.01557173131852944</v>
+      </c>
+      <c r="AJ6">
+        <v>59.5257731958767</v>
+      </c>
+      <c r="AK6">
+        <v>-1.175967413441955</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>-0.2503703703703704</v>
+      </c>
+      <c r="AP6">
+        <v>8.554074074074073</v>
       </c>
     </row>
   </sheetData>
